--- a/PCBs/core/MakerPnPControl-core_variant1_cpl.xlsx
+++ b/PCBs/core/MakerPnPControl-core_variant1_cpl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hydra\Documents\DipTrace\Projects\MakerPnPControl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hydra\Documents\DipTrace\Projects\MakerPnPControl\PCBs\core\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDE2440-27A9-41F0-8E58-604B7BB312D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C23BE13-53E6-4390-A9B5-18A11C909174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29865" yWindow="8985" windowWidth="25155" windowHeight="21300" xr2:uid="{5C73AB7E-0ECA-4E12-BEC9-2B5752DC5265}"/>
+    <workbookView xWindow="25095" yWindow="750" windowWidth="30915" windowHeight="9345" xr2:uid="{5C73AB7E-0ECA-4E12-BEC9-2B5752DC5265}"/>
   </bookViews>
   <sheets>
     <sheet name="MakerPnPControl-core_variant1_c" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="287">
   <si>
     <t>RefDes</t>
   </si>
@@ -889,6 +889,12 @@
   </si>
   <si>
     <t>Mid Y</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>SMF5.0A</t>
   </si>
 </sst>
 </file>
@@ -1749,7 +1755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CEF3696-62BC-47FC-B107-AE6F13D0BC58}">
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1781,11 +1787,11 @@
       </c>
       <c r="B2">
         <f>Sheet1!F2</f>
-        <v>15.8</v>
+        <v>12.6</v>
       </c>
       <c r="C2">
         <f>Sheet1!G2</f>
-        <v>37.700000000000003</v>
+        <v>34.274999999999999</v>
       </c>
       <c r="D2" t="str">
         <f>Sheet1!E2</f>
@@ -1825,7 +1831,7 @@
       </c>
       <c r="B4">
         <f>Sheet1!F4</f>
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="C4">
         <f>Sheet1!G4</f>
@@ -1913,7 +1919,7 @@
       </c>
       <c r="B8">
         <f>Sheet1!F8</f>
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="C8">
         <f>Sheet1!G8</f>
@@ -2001,7 +2007,7 @@
       </c>
       <c r="B12">
         <f>Sheet1!F12</f>
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="C12">
         <f>Sheet1!G12</f>
@@ -3801,15 +3807,15 @@
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="str">
         <f>Sheet1!A94</f>
-        <v>J1</v>
+        <v>E1</v>
       </c>
       <c r="B94">
         <f>Sheet1!F94</f>
-        <v>12.875</v>
+        <v>26.824999999999999</v>
       </c>
       <c r="C94">
         <f>Sheet1!G94</f>
-        <v>42.575000000000003</v>
+        <v>18.5</v>
       </c>
       <c r="D94" t="str">
         <f>Sheet1!E94</f>
@@ -3817,21 +3823,21 @@
       </c>
       <c r="E94">
         <f>ROUND(Sheet1!H94,0)</f>
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="str">
         <f>Sheet1!A95</f>
-        <v>J402</v>
+        <v>J1</v>
       </c>
       <c r="B95">
         <f>Sheet1!F95</f>
-        <v>27.5</v>
+        <v>12.875</v>
       </c>
       <c r="C95">
         <f>Sheet1!G95</f>
-        <v>26</v>
+        <v>42.575000000000003</v>
       </c>
       <c r="D95" t="str">
         <f>Sheet1!E95</f>
@@ -3845,15 +3851,15 @@
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="str">
         <f>Sheet1!A96</f>
-        <v>J403</v>
+        <v>J402</v>
       </c>
       <c r="B96">
         <f>Sheet1!F96</f>
-        <v>57.5</v>
+        <v>27.5</v>
       </c>
       <c r="C96">
         <f>Sheet1!G96</f>
-        <v>19.3</v>
+        <v>26</v>
       </c>
       <c r="D96" t="str">
         <f>Sheet1!E96</f>
@@ -3861,91 +3867,91 @@
       </c>
       <c r="E96">
         <f>ROUND(Sheet1!H96,0)</f>
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="str">
         <f>Sheet1!A97</f>
-        <v>J404</v>
+        <v>J403</v>
       </c>
       <c r="B97">
         <f>Sheet1!F97</f>
-        <v>17.5</v>
+        <v>57.5</v>
       </c>
       <c r="C97">
         <f>Sheet1!G97</f>
-        <v>48.5</v>
+        <v>19.3</v>
       </c>
       <c r="D97" t="str">
         <f>Sheet1!E97</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E97">
         <f>ROUND(Sheet1!H97,0)</f>
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="str">
         <f>Sheet1!A98</f>
-        <v>J405</v>
+        <v>J404</v>
       </c>
       <c r="B98">
         <f>Sheet1!F98</f>
-        <v>78.8</v>
+        <v>17.5</v>
       </c>
       <c r="C98">
         <f>Sheet1!G98</f>
-        <v>26.6</v>
+        <v>48.5</v>
       </c>
       <c r="D98" t="str">
         <f>Sheet1!E98</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E98">
         <f>ROUND(Sheet1!H98,0)</f>
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="str">
         <f>Sheet1!A99</f>
-        <v>J406</v>
+        <v>J405</v>
       </c>
       <c r="B99">
         <f>Sheet1!F99</f>
-        <v>97.5</v>
+        <v>78.8</v>
       </c>
       <c r="C99">
         <f>Sheet1!G99</f>
-        <v>48.5</v>
+        <v>26.6</v>
       </c>
       <c r="D99" t="str">
         <f>Sheet1!E99</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E99">
         <f>ROUND(Sheet1!H99,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="str">
         <f>Sheet1!A100</f>
-        <v>J407</v>
+        <v>J406</v>
       </c>
       <c r="B100">
         <f>Sheet1!F100</f>
-        <v>101.797</v>
+        <v>97.5</v>
       </c>
       <c r="C100">
         <f>Sheet1!G100</f>
-        <v>17.100000000000001</v>
+        <v>48.5</v>
       </c>
       <c r="D100" t="str">
         <f>Sheet1!E100</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E100">
         <f>ROUND(Sheet1!H100,0)</f>
@@ -3955,15 +3961,15 @@
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="str">
         <f>Sheet1!A101</f>
-        <v>J408</v>
+        <v>J407</v>
       </c>
       <c r="B101">
         <f>Sheet1!F101</f>
-        <v>36.200000000000003</v>
+        <v>101.797</v>
       </c>
       <c r="C101">
         <f>Sheet1!G101</f>
-        <v>26.6</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="D101" t="str">
         <f>Sheet1!E101</f>
@@ -3971,105 +3977,105 @@
       </c>
       <c r="E101">
         <f>ROUND(Sheet1!H101,0)</f>
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="str">
         <f>Sheet1!A102</f>
-        <v>J409</v>
+        <v>J408</v>
       </c>
       <c r="B102">
         <f>Sheet1!F102</f>
-        <v>32.5</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="C102">
         <f>Sheet1!G102</f>
-        <v>14.5</v>
+        <v>26.6</v>
       </c>
       <c r="D102" t="str">
         <f>Sheet1!E102</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E102">
         <f>ROUND(Sheet1!H102,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="str">
         <f>Sheet1!A103</f>
-        <v>J410</v>
+        <v>J409</v>
       </c>
       <c r="B103">
         <f>Sheet1!F103</f>
-        <v>103.25</v>
+        <v>32.5</v>
       </c>
       <c r="C103">
         <f>Sheet1!G103</f>
-        <v>41.55</v>
+        <v>14.5</v>
       </c>
       <c r="D103" t="str">
         <f>Sheet1!E103</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E103">
         <f>ROUND(Sheet1!H103,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="str">
         <f>Sheet1!A104</f>
-        <v>J411</v>
+        <v>J410</v>
       </c>
       <c r="B104">
         <f>Sheet1!F104</f>
-        <v>82.5</v>
+        <v>103.25</v>
       </c>
       <c r="C104">
         <f>Sheet1!G104</f>
-        <v>14.5</v>
+        <v>41.55</v>
       </c>
       <c r="D104" t="str">
         <f>Sheet1!E104</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E104">
         <f>ROUND(Sheet1!H104,0)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="str">
         <f>Sheet1!A105</f>
-        <v>J601</v>
+        <v>J411</v>
       </c>
       <c r="B105">
         <f>Sheet1!F105</f>
-        <v>50.75</v>
+        <v>82.5</v>
       </c>
       <c r="C105">
         <f>Sheet1!G105</f>
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="D105" t="str">
         <f>Sheet1!E105</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E105">
         <f>ROUND(Sheet1!H105,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="str">
         <f>Sheet1!A106</f>
-        <v>J602</v>
+        <v>J601</v>
       </c>
       <c r="B106">
         <f>Sheet1!F106</f>
-        <v>64.25</v>
+        <v>50.75</v>
       </c>
       <c r="C106">
         <f>Sheet1!G106</f>
@@ -4087,15 +4093,15 @@
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="str">
         <f>Sheet1!A107</f>
-        <v>L1</v>
+        <v>J602</v>
       </c>
       <c r="B107">
         <f>Sheet1!F107</f>
-        <v>17.600000000000001</v>
+        <v>64.25</v>
       </c>
       <c r="C107">
         <f>Sheet1!G107</f>
-        <v>29.5</v>
+        <v>13.5</v>
       </c>
       <c r="D107" t="str">
         <f>Sheet1!E107</f>
@@ -4103,13 +4109,13 @@
       </c>
       <c r="E107">
         <f>ROUND(Sheet1!H107,0)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="str">
         <f>Sheet1!A108</f>
-        <v>L2</v>
+        <v>L1</v>
       </c>
       <c r="B108">
         <f>Sheet1!F108</f>
@@ -4117,7 +4123,7 @@
       </c>
       <c r="C108">
         <f>Sheet1!G108</f>
-        <v>21.2</v>
+        <v>29.5</v>
       </c>
       <c r="D108" t="str">
         <f>Sheet1!E108</f>
@@ -4131,7 +4137,7 @@
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="str">
         <f>Sheet1!A109</f>
-        <v>L3</v>
+        <v>L2</v>
       </c>
       <c r="B109">
         <f>Sheet1!F109</f>
@@ -4139,7 +4145,7 @@
       </c>
       <c r="C109">
         <f>Sheet1!G109</f>
-        <v>12.9</v>
+        <v>21.2</v>
       </c>
       <c r="D109" t="str">
         <f>Sheet1!E109</f>
@@ -4153,15 +4159,15 @@
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="str">
         <f>Sheet1!A110</f>
-        <v>L101</v>
+        <v>L3</v>
       </c>
       <c r="B110">
         <f>Sheet1!F110</f>
-        <v>51.1</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="C110">
         <f>Sheet1!G110</f>
-        <v>51.225000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="D110" t="str">
         <f>Sheet1!E110</f>
@@ -4169,25 +4175,25 @@
       </c>
       <c r="E110">
         <f>ROUND(Sheet1!H110,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="str">
         <f>Sheet1!A111</f>
-        <v>R1</v>
+        <v>L101</v>
       </c>
       <c r="B111">
         <f>Sheet1!F111</f>
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="C111">
         <f>Sheet1!G111</f>
-        <v>13.5</v>
+        <v>51.225000000000001</v>
       </c>
       <c r="D111" t="str">
         <f>Sheet1!E111</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E111">
         <f>ROUND(Sheet1!H111,0)</f>
@@ -4197,37 +4203,37 @@
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="str">
         <f>Sheet1!A112</f>
-        <v>R2</v>
+        <v>R1</v>
       </c>
       <c r="B112">
         <f>Sheet1!F112</f>
-        <v>21.1</v>
+        <v>46.5</v>
       </c>
       <c r="C112">
         <f>Sheet1!G112</f>
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="D112" t="str">
         <f>Sheet1!E112</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E112">
         <f>ROUND(Sheet1!H112,0)</f>
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="str">
         <f>Sheet1!A113</f>
-        <v>R3</v>
+        <v>R2</v>
       </c>
       <c r="B113">
         <f>Sheet1!F113</f>
-        <v>21.15</v>
+        <v>21.1</v>
       </c>
       <c r="C113">
         <f>Sheet1!G113</f>
-        <v>12.95</v>
+        <v>16.7</v>
       </c>
       <c r="D113" t="str">
         <f>Sheet1!E113</f>
@@ -4241,15 +4247,15 @@
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="str">
         <f>Sheet1!A114</f>
-        <v>R4</v>
+        <v>R3</v>
       </c>
       <c r="B114">
         <f>Sheet1!F114</f>
-        <v>48.475000000000001</v>
+        <v>21.15</v>
       </c>
       <c r="C114">
         <f>Sheet1!G114</f>
-        <v>26.425000000000001</v>
+        <v>12.95</v>
       </c>
       <c r="D114" t="str">
         <f>Sheet1!E114</f>
@@ -4257,13 +4263,13 @@
       </c>
       <c r="E114">
         <f>ROUND(Sheet1!H114,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="str">
         <f>Sheet1!A115</f>
-        <v>R5</v>
+        <v>R4</v>
       </c>
       <c r="B115">
         <f>Sheet1!F115</f>
@@ -4271,7 +4277,7 @@
       </c>
       <c r="C115">
         <f>Sheet1!G115</f>
-        <v>28.225000000000001</v>
+        <v>26.425000000000001</v>
       </c>
       <c r="D115" t="str">
         <f>Sheet1!E115</f>
@@ -4279,21 +4285,21 @@
       </c>
       <c r="E115">
         <f>ROUND(Sheet1!H115,0)</f>
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="str">
         <f>Sheet1!A116</f>
-        <v>R6</v>
+        <v>R5</v>
       </c>
       <c r="B116">
         <f>Sheet1!F116</f>
-        <v>14.1</v>
+        <v>48.475000000000001</v>
       </c>
       <c r="C116">
         <f>Sheet1!G116</f>
-        <v>32.450000000000003</v>
+        <v>28.225000000000001</v>
       </c>
       <c r="D116" t="str">
         <f>Sheet1!E116</f>
@@ -4301,21 +4307,21 @@
       </c>
       <c r="E116">
         <f>ROUND(Sheet1!H116,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="str">
         <f>Sheet1!A117</f>
-        <v>R7</v>
+        <v>R6</v>
       </c>
       <c r="B117">
         <f>Sheet1!F117</f>
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="C117">
         <f>Sheet1!G117</f>
-        <v>33.450000000000003</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="D117" t="str">
         <f>Sheet1!E117</f>
@@ -4329,15 +4335,15 @@
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="str">
         <f>Sheet1!A118</f>
-        <v>R8</v>
+        <v>R7</v>
       </c>
       <c r="B118">
         <f>Sheet1!F118</f>
-        <v>12.1</v>
+        <v>14.6</v>
       </c>
       <c r="C118">
         <f>Sheet1!G118</f>
-        <v>32.450000000000003</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="D118" t="str">
         <f>Sheet1!E118</f>
@@ -4345,21 +4351,21 @@
       </c>
       <c r="E118">
         <f>ROUND(Sheet1!H118,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="str">
         <f>Sheet1!A119</f>
-        <v>R9</v>
+        <v>R8</v>
       </c>
       <c r="B119">
         <f>Sheet1!F119</f>
-        <v>14.1</v>
+        <v>12.6</v>
       </c>
       <c r="C119">
         <f>Sheet1!G119</f>
-        <v>24.15</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="D119" t="str">
         <f>Sheet1!E119</f>
@@ -4367,21 +4373,21 @@
       </c>
       <c r="E119">
         <f>ROUND(Sheet1!H119,0)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="str">
         <f>Sheet1!A120</f>
-        <v>R10</v>
+        <v>R9</v>
       </c>
       <c r="B120">
         <f>Sheet1!F120</f>
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="C120">
         <f>Sheet1!G120</f>
-        <v>25.15</v>
+        <v>24.15</v>
       </c>
       <c r="D120" t="str">
         <f>Sheet1!E120</f>
@@ -4395,15 +4401,15 @@
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="str">
         <f>Sheet1!A121</f>
-        <v>R11</v>
+        <v>R10</v>
       </c>
       <c r="B121">
         <f>Sheet1!F121</f>
-        <v>12.1</v>
+        <v>14.6</v>
       </c>
       <c r="C121">
         <f>Sheet1!G121</f>
-        <v>24.15</v>
+        <v>25.15</v>
       </c>
       <c r="D121" t="str">
         <f>Sheet1!E121</f>
@@ -4411,21 +4417,21 @@
       </c>
       <c r="E121">
         <f>ROUND(Sheet1!H121,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="str">
         <f>Sheet1!A122</f>
-        <v>R12</v>
+        <v>R11</v>
       </c>
       <c r="B122">
         <f>Sheet1!F122</f>
-        <v>14.1</v>
+        <v>12.6</v>
       </c>
       <c r="C122">
         <f>Sheet1!G122</f>
-        <v>15.85</v>
+        <v>24.15</v>
       </c>
       <c r="D122" t="str">
         <f>Sheet1!E122</f>
@@ -4433,21 +4439,21 @@
       </c>
       <c r="E122">
         <f>ROUND(Sheet1!H122,0)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="str">
         <f>Sheet1!A123</f>
-        <v>R13</v>
+        <v>R12</v>
       </c>
       <c r="B123">
         <f>Sheet1!F123</f>
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="C123">
         <f>Sheet1!G123</f>
-        <v>16.850000000000001</v>
+        <v>15.85</v>
       </c>
       <c r="D123" t="str">
         <f>Sheet1!E123</f>
@@ -4461,15 +4467,15 @@
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="str">
         <f>Sheet1!A124</f>
-        <v>R14</v>
+        <v>R13</v>
       </c>
       <c r="B124">
         <f>Sheet1!F124</f>
-        <v>12.1</v>
+        <v>14.6</v>
       </c>
       <c r="C124">
         <f>Sheet1!G124</f>
-        <v>15.85</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="D124" t="str">
         <f>Sheet1!E124</f>
@@ -4477,21 +4483,21 @@
       </c>
       <c r="E124">
         <f>ROUND(Sheet1!H124,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="str">
         <f>Sheet1!A125</f>
-        <v>R101</v>
+        <v>R14</v>
       </c>
       <c r="B125">
         <f>Sheet1!F125</f>
-        <v>51.1</v>
+        <v>12.6</v>
       </c>
       <c r="C125">
         <f>Sheet1!G125</f>
-        <v>48.55</v>
+        <v>15.85</v>
       </c>
       <c r="D125" t="str">
         <f>Sheet1!E125</f>
@@ -4499,101 +4505,101 @@
       </c>
       <c r="E125">
         <f>ROUND(Sheet1!H125,0)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="str">
         <f>Sheet1!A126</f>
-        <v>R102</v>
+        <v>R101</v>
       </c>
       <c r="B126">
         <f>Sheet1!F126</f>
-        <v>50.35</v>
+        <v>51.1</v>
       </c>
       <c r="C126">
         <f>Sheet1!G126</f>
-        <v>53.174999999999997</v>
+        <v>48.55</v>
       </c>
       <c r="D126" t="str">
         <f>Sheet1!E126</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E126">
         <f>ROUND(Sheet1!H126,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="str">
         <f>Sheet1!A127</f>
-        <v>R103</v>
+        <v>R102</v>
       </c>
       <c r="B127">
         <f>Sheet1!F127</f>
-        <v>65.525000000000006</v>
+        <v>50.35</v>
       </c>
       <c r="C127">
         <f>Sheet1!G127</f>
-        <v>53.575000000000003</v>
+        <v>53.174999999999997</v>
       </c>
       <c r="D127" t="str">
         <f>Sheet1!E127</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E127">
         <f>ROUND(Sheet1!H127,0)</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="str">
         <f>Sheet1!A128</f>
-        <v>R104</v>
+        <v>R103</v>
       </c>
       <c r="B128">
         <f>Sheet1!F128</f>
-        <v>53.274999999999999</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="C128">
         <f>Sheet1!G128</f>
-        <v>48.375</v>
+        <v>53.575000000000003</v>
       </c>
       <c r="D128" t="str">
         <f>Sheet1!E128</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E128">
         <f>ROUND(Sheet1!H128,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="str">
         <f>Sheet1!A129</f>
-        <v>R105</v>
+        <v>R104</v>
       </c>
       <c r="B129">
         <f>Sheet1!F129</f>
-        <v>74.900000000000006</v>
+        <v>53.274999999999999</v>
       </c>
       <c r="C129">
         <f>Sheet1!G129</f>
-        <v>32.549999999999997</v>
+        <v>48.375</v>
       </c>
       <c r="D129" t="str">
         <f>Sheet1!E129</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E129">
         <f>ROUND(Sheet1!H129,0)</f>
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="str">
         <f>Sheet1!A130</f>
-        <v>R106</v>
+        <v>R105</v>
       </c>
       <c r="B130">
         <f>Sheet1!F130</f>
@@ -4601,7 +4607,7 @@
       </c>
       <c r="C130">
         <f>Sheet1!G130</f>
-        <v>33.450000000000003</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="D130" t="str">
         <f>Sheet1!E130</f>
@@ -4615,15 +4621,15 @@
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="str">
         <f>Sheet1!A131</f>
-        <v>R107</v>
+        <v>R106</v>
       </c>
       <c r="B131">
         <f>Sheet1!F131</f>
-        <v>75.2</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="C131">
         <f>Sheet1!G131</f>
-        <v>29.05</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="D131" t="str">
         <f>Sheet1!E131</f>
@@ -4631,43 +4637,43 @@
       </c>
       <c r="E131">
         <f>ROUND(Sheet1!H131,0)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="str">
         <f>Sheet1!A132</f>
-        <v>R108</v>
+        <v>R107</v>
       </c>
       <c r="B132">
         <f>Sheet1!F132</f>
-        <v>66.8</v>
+        <v>75.2</v>
       </c>
       <c r="C132">
         <f>Sheet1!G132</f>
-        <v>31.3</v>
+        <v>29.05</v>
       </c>
       <c r="D132" t="str">
         <f>Sheet1!E132</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E132">
         <f>ROUND(Sheet1!H132,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="str">
         <f>Sheet1!A133</f>
-        <v>R109</v>
+        <v>R108</v>
       </c>
       <c r="B133">
         <f>Sheet1!F133</f>
-        <v>63.9</v>
+        <v>66.8</v>
       </c>
       <c r="C133">
         <f>Sheet1!G133</f>
-        <v>35.5</v>
+        <v>31.3</v>
       </c>
       <c r="D133" t="str">
         <f>Sheet1!E133</f>
@@ -4675,21 +4681,21 @@
       </c>
       <c r="E133">
         <f>ROUND(Sheet1!H133,0)</f>
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="str">
         <f>Sheet1!A134</f>
-        <v>R110</v>
+        <v>R109</v>
       </c>
       <c r="B134">
         <f>Sheet1!F134</f>
-        <v>45.4</v>
+        <v>63.9</v>
       </c>
       <c r="C134">
         <f>Sheet1!G134</f>
-        <v>28.3</v>
+        <v>35.5</v>
       </c>
       <c r="D134" t="str">
         <f>Sheet1!E134</f>
@@ -4697,13 +4703,13 @@
       </c>
       <c r="E134">
         <f>ROUND(Sheet1!H134,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="str">
         <f>Sheet1!A135</f>
-        <v>R111</v>
+        <v>R110</v>
       </c>
       <c r="B135">
         <f>Sheet1!F135</f>
@@ -4711,7 +4717,7 @@
       </c>
       <c r="C135">
         <f>Sheet1!G135</f>
-        <v>33.1</v>
+        <v>28.3</v>
       </c>
       <c r="D135" t="str">
         <f>Sheet1!E135</f>
@@ -4725,15 +4731,15 @@
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="str">
         <f>Sheet1!A136</f>
-        <v>R112</v>
+        <v>R111</v>
       </c>
       <c r="B136">
         <f>Sheet1!F136</f>
-        <v>60.7</v>
+        <v>45.4</v>
       </c>
       <c r="C136">
         <f>Sheet1!G136</f>
-        <v>36.75</v>
+        <v>33.1</v>
       </c>
       <c r="D136" t="str">
         <f>Sheet1!E136</f>
@@ -4747,19 +4753,19 @@
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="str">
         <f>Sheet1!A137</f>
-        <v>R113</v>
+        <v>R112</v>
       </c>
       <c r="B137">
         <f>Sheet1!F137</f>
-        <v>86.5</v>
+        <v>60.7</v>
       </c>
       <c r="C137">
         <f>Sheet1!G137</f>
-        <v>26.25</v>
+        <v>36.75</v>
       </c>
       <c r="D137" t="str">
         <f>Sheet1!E137</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E137">
         <f>ROUND(Sheet1!H137,0)</f>
@@ -4769,37 +4775,37 @@
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="str">
         <f>Sheet1!A138</f>
-        <v>R114</v>
+        <v>R113</v>
       </c>
       <c r="B138">
         <f>Sheet1!F138</f>
-        <v>45.4</v>
+        <v>86.5</v>
       </c>
       <c r="C138">
         <f>Sheet1!G138</f>
-        <v>30</v>
+        <v>26.25</v>
       </c>
       <c r="D138" t="str">
         <f>Sheet1!E138</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E138">
         <f>ROUND(Sheet1!H138,0)</f>
-        <v>-180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="str">
         <f>Sheet1!A139</f>
-        <v>R115</v>
+        <v>R114</v>
       </c>
       <c r="B139">
         <f>Sheet1!F139</f>
-        <v>66.8</v>
+        <v>45.4</v>
       </c>
       <c r="C139">
         <f>Sheet1!G139</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D139" t="str">
         <f>Sheet1!E139</f>
@@ -4807,35 +4813,35 @@
       </c>
       <c r="E139">
         <f>ROUND(Sheet1!H139,0)</f>
-        <v>-90</v>
+        <v>-180</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="str">
         <f>Sheet1!A140</f>
-        <v>R116</v>
+        <v>R115</v>
       </c>
       <c r="B140">
         <f>Sheet1!F140</f>
-        <v>86.5</v>
+        <v>66.8</v>
       </c>
       <c r="C140">
         <f>Sheet1!G140</f>
-        <v>28.75</v>
+        <v>28</v>
       </c>
       <c r="D140" t="str">
         <f>Sheet1!E140</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E140">
         <f>ROUND(Sheet1!H140,0)</f>
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="str">
         <f>Sheet1!A141</f>
-        <v>R117</v>
+        <v>R116</v>
       </c>
       <c r="B141">
         <f>Sheet1!F141</f>
@@ -4843,7 +4849,7 @@
       </c>
       <c r="C141">
         <f>Sheet1!G141</f>
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="D141" t="str">
         <f>Sheet1!E141</f>
@@ -4857,37 +4863,37 @@
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="str">
         <f>Sheet1!A142</f>
-        <v>R118</v>
+        <v>R117</v>
       </c>
       <c r="B142">
         <f>Sheet1!F142</f>
-        <v>71.900000000000006</v>
+        <v>86.5</v>
       </c>
       <c r="C142">
         <f>Sheet1!G142</f>
-        <v>37.200000000000003</v>
+        <v>27.75</v>
       </c>
       <c r="D142" t="str">
         <f>Sheet1!E142</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E142">
         <f>ROUND(Sheet1!H142,0)</f>
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="str">
         <f>Sheet1!A143</f>
-        <v>R119</v>
+        <v>R118</v>
       </c>
       <c r="B143">
         <f>Sheet1!F143</f>
-        <v>71.3</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="C143">
         <f>Sheet1!G143</f>
-        <v>35.25</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D143" t="str">
         <f>Sheet1!E143</f>
@@ -4901,11 +4907,11 @@
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="str">
         <f>Sheet1!A144</f>
-        <v>R120</v>
+        <v>R119</v>
       </c>
       <c r="B144">
         <f>Sheet1!F144</f>
-        <v>72.5</v>
+        <v>71.3</v>
       </c>
       <c r="C144">
         <f>Sheet1!G144</f>
@@ -4923,37 +4929,37 @@
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="str">
         <f>Sheet1!A145</f>
-        <v>R121</v>
+        <v>R120</v>
       </c>
       <c r="B145">
         <f>Sheet1!F145</f>
-        <v>86.5</v>
+        <v>72.5</v>
       </c>
       <c r="C145">
         <f>Sheet1!G145</f>
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
       <c r="D145" t="str">
         <f>Sheet1!E145</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E145">
         <f>ROUND(Sheet1!H145,0)</f>
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="str">
         <f>Sheet1!A146</f>
-        <v>R122</v>
+        <v>R121</v>
       </c>
       <c r="B146">
         <f>Sheet1!F146</f>
-        <v>72.05</v>
+        <v>86.5</v>
       </c>
       <c r="C146">
         <f>Sheet1!G146</f>
-        <v>29.05</v>
+        <v>34.25</v>
       </c>
       <c r="D146" t="str">
         <f>Sheet1!E146</f>
@@ -4961,39 +4967,39 @@
       </c>
       <c r="E146">
         <f>ROUND(Sheet1!H146,0)</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="str">
         <f>Sheet1!A147</f>
-        <v>R123</v>
+        <v>R122</v>
       </c>
       <c r="B147">
         <f>Sheet1!F147</f>
-        <v>73.099999999999994</v>
+        <v>72.05</v>
       </c>
       <c r="C147">
         <f>Sheet1!G147</f>
-        <v>37.200000000000003</v>
+        <v>29.05</v>
       </c>
       <c r="D147" t="str">
         <f>Sheet1!E147</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E147">
         <f>ROUND(Sheet1!H147,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="str">
         <f>Sheet1!A148</f>
-        <v>R124</v>
+        <v>R123</v>
       </c>
       <c r="B148">
         <f>Sheet1!F148</f>
-        <v>70.7</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="C148">
         <f>Sheet1!G148</f>
@@ -5011,19 +5017,19 @@
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="str">
         <f>Sheet1!A149</f>
-        <v>R125</v>
+        <v>R124</v>
       </c>
       <c r="B149">
         <f>Sheet1!F149</f>
-        <v>75.25</v>
+        <v>70.7</v>
       </c>
       <c r="C149">
         <f>Sheet1!G149</f>
-        <v>23.324999999999999</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D149" t="str">
         <f>Sheet1!E149</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E149">
         <f>ROUND(Sheet1!H149,0)</f>
@@ -5033,37 +5039,37 @@
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="str">
         <f>Sheet1!A150</f>
-        <v>R126</v>
+        <v>R125</v>
       </c>
       <c r="B150">
         <f>Sheet1!F150</f>
-        <v>57.35</v>
+        <v>75.25</v>
       </c>
       <c r="C150">
         <f>Sheet1!G150</f>
-        <v>37.200000000000003</v>
+        <v>23.324999999999999</v>
       </c>
       <c r="D150" t="str">
         <f>Sheet1!E150</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E150">
         <f>ROUND(Sheet1!H150,0)</f>
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="str">
         <f>Sheet1!A151</f>
-        <v>R127</v>
+        <v>R126</v>
       </c>
       <c r="B151">
         <f>Sheet1!F151</f>
-        <v>64.7</v>
+        <v>57.35</v>
       </c>
       <c r="C151">
         <f>Sheet1!G151</f>
-        <v>22.8</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D151" t="str">
         <f>Sheet1!E151</f>
@@ -5077,37 +5083,37 @@
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="str">
         <f>Sheet1!A152</f>
-        <v>R128</v>
+        <v>R127</v>
       </c>
       <c r="B152">
         <f>Sheet1!F152</f>
-        <v>73.099999999999994</v>
+        <v>64.7</v>
       </c>
       <c r="C152">
         <f>Sheet1!G152</f>
-        <v>29.05</v>
+        <v>22.8</v>
       </c>
       <c r="D152" t="str">
         <f>Sheet1!E152</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E152">
         <f>ROUND(Sheet1!H152,0)</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="str">
         <f>Sheet1!A153</f>
-        <v>R129</v>
+        <v>R128</v>
       </c>
       <c r="B153">
         <f>Sheet1!F153</f>
-        <v>92</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="C153">
         <f>Sheet1!G153</f>
-        <v>38</v>
+        <v>29.05</v>
       </c>
       <c r="D153" t="str">
         <f>Sheet1!E153</f>
@@ -5115,21 +5121,21 @@
       </c>
       <c r="E153">
         <f>ROUND(Sheet1!H153,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="str">
         <f>Sheet1!A154</f>
-        <v>R130</v>
+        <v>R129</v>
       </c>
       <c r="B154">
         <f>Sheet1!F154</f>
-        <v>73.099999999999994</v>
+        <v>92</v>
       </c>
       <c r="C154">
         <f>Sheet1!G154</f>
-        <v>34.4</v>
+        <v>38</v>
       </c>
       <c r="D154" t="str">
         <f>Sheet1!E154</f>
@@ -5143,11 +5149,11 @@
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="str">
         <f>Sheet1!A155</f>
-        <v>R131</v>
+        <v>R130</v>
       </c>
       <c r="B155">
         <f>Sheet1!F155</f>
-        <v>74.900000000000006</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="C155">
         <f>Sheet1!G155</f>
@@ -5165,15 +5171,15 @@
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="str">
         <f>Sheet1!A156</f>
-        <v>R132</v>
+        <v>R131</v>
       </c>
       <c r="B156">
         <f>Sheet1!F156</f>
-        <v>86.5</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="C156">
         <f>Sheet1!G156</f>
-        <v>31.15</v>
+        <v>34.4</v>
       </c>
       <c r="D156" t="str">
         <f>Sheet1!E156</f>
@@ -5181,13 +5187,13 @@
       </c>
       <c r="E156">
         <f>ROUND(Sheet1!H156,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="str">
         <f>Sheet1!A157</f>
-        <v>R133</v>
+        <v>R132</v>
       </c>
       <c r="B157">
         <f>Sheet1!F157</f>
@@ -5195,7 +5201,7 @@
       </c>
       <c r="C157">
         <f>Sheet1!G157</f>
-        <v>30.15</v>
+        <v>31.15</v>
       </c>
       <c r="D157" t="str">
         <f>Sheet1!E157</f>
@@ -5209,51 +5215,51 @@
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="str">
         <f>Sheet1!A158</f>
-        <v>R134</v>
+        <v>R133</v>
       </c>
       <c r="B158">
         <f>Sheet1!F158</f>
-        <v>94</v>
+        <v>86.5</v>
       </c>
       <c r="C158">
         <f>Sheet1!G158</f>
-        <v>24.15</v>
+        <v>30.15</v>
       </c>
       <c r="D158" t="str">
         <f>Sheet1!E158</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E158">
         <f>ROUND(Sheet1!H158,0)</f>
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="str">
         <f>Sheet1!A159</f>
-        <v>R135</v>
+        <v>R134</v>
       </c>
       <c r="B159">
         <f>Sheet1!F159</f>
-        <v>48.4</v>
+        <v>94</v>
       </c>
       <c r="C159">
         <f>Sheet1!G159</f>
-        <v>47.15</v>
+        <v>24.15</v>
       </c>
       <c r="D159" t="str">
         <f>Sheet1!E159</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E159">
         <f>ROUND(Sheet1!H159,0)</f>
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="str">
         <f>Sheet1!A160</f>
-        <v>R136</v>
+        <v>R135</v>
       </c>
       <c r="B160">
         <f>Sheet1!F160</f>
@@ -5261,7 +5267,7 @@
       </c>
       <c r="C160">
         <f>Sheet1!G160</f>
-        <v>46</v>
+        <v>47.15</v>
       </c>
       <c r="D160" t="str">
         <f>Sheet1!E160</f>
@@ -5275,15 +5281,15 @@
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="str">
         <f>Sheet1!A161</f>
-        <v>R137</v>
+        <v>R136</v>
       </c>
       <c r="B161">
         <f>Sheet1!F161</f>
-        <v>31.3</v>
+        <v>48.4</v>
       </c>
       <c r="C161">
         <f>Sheet1!G161</f>
-        <v>32.450000000000003</v>
+        <v>46</v>
       </c>
       <c r="D161" t="str">
         <f>Sheet1!E161</f>
@@ -5291,21 +5297,21 @@
       </c>
       <c r="E161">
         <f>ROUND(Sheet1!H161,0)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="str">
         <f>Sheet1!A162</f>
-        <v>R138</v>
+        <v>R137</v>
       </c>
       <c r="B162">
         <f>Sheet1!F162</f>
-        <v>82.45</v>
+        <v>31.3</v>
       </c>
       <c r="C162">
         <f>Sheet1!G162</f>
-        <v>23.324999999999999</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="D162" t="str">
         <f>Sheet1!E162</f>
@@ -5319,15 +5325,15 @@
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="str">
         <f>Sheet1!A163</f>
-        <v>R139</v>
+        <v>R138</v>
       </c>
       <c r="B163">
         <f>Sheet1!F163</f>
-        <v>32.5</v>
+        <v>82.45</v>
       </c>
       <c r="C163">
         <f>Sheet1!G163</f>
-        <v>23.45</v>
+        <v>23.324999999999999</v>
       </c>
       <c r="D163" t="str">
         <f>Sheet1!E163</f>
@@ -5341,15 +5347,15 @@
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="str">
         <f>Sheet1!A164</f>
-        <v>R401</v>
+        <v>R139</v>
       </c>
       <c r="B164">
         <f>Sheet1!F164</f>
-        <v>26.125</v>
+        <v>32.5</v>
       </c>
       <c r="C164">
         <f>Sheet1!G164</f>
-        <v>21.875</v>
+        <v>23.45</v>
       </c>
       <c r="D164" t="str">
         <f>Sheet1!E164</f>
@@ -5357,25 +5363,25 @@
       </c>
       <c r="E164">
         <f>ROUND(Sheet1!H164,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="str">
         <f>Sheet1!A165</f>
-        <v>R402</v>
+        <v>R401</v>
       </c>
       <c r="B165">
         <f>Sheet1!F165</f>
-        <v>14.025</v>
+        <v>26.125</v>
       </c>
       <c r="C165">
         <f>Sheet1!G165</f>
-        <v>58.3</v>
+        <v>21.875</v>
       </c>
       <c r="D165" t="str">
         <f>Sheet1!E165</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E165">
         <f>ROUND(Sheet1!H165,0)</f>
@@ -5385,19 +5391,19 @@
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="str">
         <f>Sheet1!A166</f>
-        <v>R403</v>
+        <v>R402</v>
       </c>
       <c r="B166">
         <f>Sheet1!F166</f>
-        <v>95.9</v>
+        <v>14.025</v>
       </c>
       <c r="C166">
         <f>Sheet1!G166</f>
-        <v>20.2</v>
+        <v>58.3</v>
       </c>
       <c r="D166" t="str">
         <f>Sheet1!E166</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E166">
         <f>ROUND(Sheet1!H166,0)</f>
@@ -5407,15 +5413,15 @@
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="str">
         <f>Sheet1!A167</f>
-        <v>R404</v>
+        <v>R403</v>
       </c>
       <c r="B167">
         <f>Sheet1!F167</f>
-        <v>86.5</v>
+        <v>95.9</v>
       </c>
       <c r="C167">
         <f>Sheet1!G167</f>
-        <v>25.25</v>
+        <v>20.2</v>
       </c>
       <c r="D167" t="str">
         <f>Sheet1!E167</f>
@@ -5423,39 +5429,39 @@
       </c>
       <c r="E167">
         <f>ROUND(Sheet1!H167,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="str">
         <f>Sheet1!A168</f>
-        <v>R405</v>
+        <v>R404</v>
       </c>
       <c r="B168">
         <f>Sheet1!F168</f>
-        <v>103.88500000000001</v>
+        <v>86.5</v>
       </c>
       <c r="C168">
         <f>Sheet1!G168</f>
-        <v>41.55</v>
+        <v>25.25</v>
       </c>
       <c r="D168" t="str">
         <f>Sheet1!E168</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E168">
         <f>ROUND(Sheet1!H168,0)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="str">
         <f>Sheet1!A169</f>
-        <v>R406</v>
+        <v>R405</v>
       </c>
       <c r="B169">
         <f>Sheet1!F169</f>
-        <v>102.61499999999999</v>
+        <v>103.88500000000001</v>
       </c>
       <c r="C169">
         <f>Sheet1!G169</f>
@@ -5473,59 +5479,59 @@
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="str">
         <f>Sheet1!A170</f>
-        <v>R407</v>
+        <v>R406</v>
       </c>
       <c r="B170">
         <f>Sheet1!F170</f>
-        <v>11.75</v>
+        <v>102.61499999999999</v>
       </c>
       <c r="C170">
         <f>Sheet1!G170</f>
-        <v>61.125</v>
+        <v>41.55</v>
       </c>
       <c r="D170" t="str">
         <f>Sheet1!E170</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E170">
         <f>ROUND(Sheet1!H170,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="str">
         <f>Sheet1!A171</f>
-        <v>R408</v>
+        <v>R407</v>
       </c>
       <c r="B171">
         <f>Sheet1!F171</f>
-        <v>44.35</v>
+        <v>11.75</v>
       </c>
       <c r="C171">
         <f>Sheet1!G171</f>
-        <v>15.9</v>
+        <v>61.125</v>
       </c>
       <c r="D171" t="str">
         <f>Sheet1!E171</f>
-        <v>Bottom</v>
+        <v>Top</v>
       </c>
       <c r="E171">
         <f>ROUND(Sheet1!H171,0)</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="str">
         <f>Sheet1!A172</f>
-        <v>R409</v>
+        <v>R408</v>
       </c>
       <c r="B172">
         <f>Sheet1!F172</f>
-        <v>70.924999999999997</v>
+        <v>44.35</v>
       </c>
       <c r="C172">
         <f>Sheet1!G172</f>
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="D172" t="str">
         <f>Sheet1!E172</f>
@@ -5539,37 +5545,37 @@
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="str">
         <f>Sheet1!A173</f>
-        <v>R601</v>
+        <v>R409</v>
       </c>
       <c r="B173">
         <f>Sheet1!F173</f>
-        <v>50.75</v>
+        <v>70.924999999999997</v>
       </c>
       <c r="C173">
         <f>Sheet1!G173</f>
-        <v>16.024999999999999</v>
+        <v>16.3</v>
       </c>
       <c r="D173" t="str">
         <f>Sheet1!E173</f>
-        <v>Top</v>
+        <v>Bottom</v>
       </c>
       <c r="E173">
         <f>ROUND(Sheet1!H173,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="str">
         <f>Sheet1!A174</f>
-        <v>R602</v>
+        <v>R601</v>
       </c>
       <c r="B174">
         <f>Sheet1!F174</f>
-        <v>66</v>
+        <v>50.75</v>
       </c>
       <c r="C174">
         <f>Sheet1!G174</f>
-        <v>17</v>
+        <v>16.024999999999999</v>
       </c>
       <c r="D174" t="str">
         <f>Sheet1!E174</f>
@@ -5577,17 +5583,17 @@
       </c>
       <c r="E174">
         <f>ROUND(Sheet1!H174,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="str">
         <f>Sheet1!A175</f>
-        <v>R603</v>
+        <v>R602</v>
       </c>
       <c r="B175">
         <f>Sheet1!F175</f>
-        <v>49.024999999999999</v>
+        <v>66</v>
       </c>
       <c r="C175">
         <f>Sheet1!G175</f>
@@ -5599,21 +5605,21 @@
       </c>
       <c r="E175">
         <f>ROUND(Sheet1!H175,0)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="str">
         <f>Sheet1!A176</f>
-        <v>R604</v>
+        <v>R603</v>
       </c>
       <c r="B176">
         <f>Sheet1!F176</f>
-        <v>64.25</v>
+        <v>49.024999999999999</v>
       </c>
       <c r="C176">
         <f>Sheet1!G176</f>
-        <v>16.024999999999999</v>
+        <v>17</v>
       </c>
       <c r="D176" t="str">
         <f>Sheet1!E176</f>
@@ -5621,21 +5627,21 @@
       </c>
       <c r="E176">
         <f>ROUND(Sheet1!H176,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="str">
         <f>Sheet1!A177</f>
-        <v>R605</v>
+        <v>R604</v>
       </c>
       <c r="B177">
         <f>Sheet1!F177</f>
-        <v>72.7</v>
+        <v>64.25</v>
       </c>
       <c r="C177">
         <f>Sheet1!G177</f>
-        <v>21.45</v>
+        <v>16.024999999999999</v>
       </c>
       <c r="D177" t="str">
         <f>Sheet1!E177</f>
@@ -5643,21 +5649,21 @@
       </c>
       <c r="E177">
         <f>ROUND(Sheet1!H177,0)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="str">
         <f>Sheet1!A178</f>
-        <v>R606</v>
+        <v>R605</v>
       </c>
       <c r="B178">
         <f>Sheet1!F178</f>
-        <v>86.2</v>
+        <v>72.7</v>
       </c>
       <c r="C178">
         <f>Sheet1!G178</f>
-        <v>17.75</v>
+        <v>21.45</v>
       </c>
       <c r="D178" t="str">
         <f>Sheet1!E178</f>
@@ -5665,21 +5671,21 @@
       </c>
       <c r="E178">
         <f>ROUND(Sheet1!H178,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="str">
         <f>Sheet1!A179</f>
-        <v>R607</v>
+        <v>R606</v>
       </c>
       <c r="B179">
         <f>Sheet1!F179</f>
-        <v>68.7</v>
+        <v>86.2</v>
       </c>
       <c r="C179">
         <f>Sheet1!G179</f>
-        <v>21.45</v>
+        <v>17.75</v>
       </c>
       <c r="D179" t="str">
         <f>Sheet1!E179</f>
@@ -5687,17 +5693,17 @@
       </c>
       <c r="E179">
         <f>ROUND(Sheet1!H179,0)</f>
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="str">
         <f>Sheet1!A180</f>
-        <v>R608</v>
+        <v>R607</v>
       </c>
       <c r="B180">
         <f>Sheet1!F180</f>
-        <v>69.7</v>
+        <v>68.7</v>
       </c>
       <c r="C180">
         <f>Sheet1!G180</f>
@@ -5709,21 +5715,21 @@
       </c>
       <c r="E180">
         <f>ROUND(Sheet1!H180,0)</f>
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="str">
         <f>Sheet1!A181</f>
-        <v>R609</v>
+        <v>R608</v>
       </c>
       <c r="B181">
         <f>Sheet1!F181</f>
-        <v>86.2</v>
+        <v>69.7</v>
       </c>
       <c r="C181">
         <f>Sheet1!G181</f>
-        <v>21.65</v>
+        <v>21.45</v>
       </c>
       <c r="D181" t="str">
         <f>Sheet1!E181</f>
@@ -5731,13 +5737,13 @@
       </c>
       <c r="E181">
         <f>ROUND(Sheet1!H181,0)</f>
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="str">
         <f>Sheet1!A182</f>
-        <v>R610</v>
+        <v>R609</v>
       </c>
       <c r="B182">
         <f>Sheet1!F182</f>
@@ -5745,7 +5751,7 @@
       </c>
       <c r="C182">
         <f>Sheet1!G182</f>
-        <v>20.7</v>
+        <v>21.65</v>
       </c>
       <c r="D182" t="str">
         <f>Sheet1!E182</f>
@@ -5753,21 +5759,21 @@
       </c>
       <c r="E182">
         <f>ROUND(Sheet1!H182,0)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="str">
         <f>Sheet1!A183</f>
-        <v>R611</v>
+        <v>R610</v>
       </c>
       <c r="B183">
         <f>Sheet1!F183</f>
-        <v>51.45</v>
+        <v>86.2</v>
       </c>
       <c r="C183">
         <f>Sheet1!G183</f>
-        <v>10.75</v>
+        <v>20.7</v>
       </c>
       <c r="D183" t="str">
         <f>Sheet1!E183</f>
@@ -5775,17 +5781,17 @@
       </c>
       <c r="E183">
         <f>ROUND(Sheet1!H183,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="str">
         <f>Sheet1!A184</f>
-        <v>R612</v>
+        <v>R611</v>
       </c>
       <c r="B184">
         <f>Sheet1!F184</f>
-        <v>63.55</v>
+        <v>51.45</v>
       </c>
       <c r="C184">
         <f>Sheet1!G184</f>
@@ -5797,21 +5803,21 @@
       </c>
       <c r="E184">
         <f>ROUND(Sheet1!H184,0)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="str">
         <f>Sheet1!A185</f>
-        <v>S401</v>
+        <v>R612</v>
       </c>
       <c r="B185">
         <f>Sheet1!F185</f>
-        <v>11.75</v>
+        <v>63.55</v>
       </c>
       <c r="C185">
         <f>Sheet1!G185</f>
-        <v>58</v>
+        <v>10.75</v>
       </c>
       <c r="D185" t="str">
         <f>Sheet1!E185</f>
@@ -5819,13 +5825,13 @@
       </c>
       <c r="E185">
         <f>ROUND(Sheet1!H185,0)</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="str">
         <f>Sheet1!A186</f>
-        <v>S402</v>
+        <v>S401</v>
       </c>
       <c r="B186">
         <f>Sheet1!F186</f>
@@ -5833,7 +5839,7 @@
       </c>
       <c r="C186">
         <f>Sheet1!G186</f>
-        <v>50.5</v>
+        <v>58</v>
       </c>
       <c r="D186" t="str">
         <f>Sheet1!E186</f>
@@ -5847,15 +5853,15 @@
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="str">
         <f>Sheet1!A187</f>
-        <v>S403</v>
+        <v>S402</v>
       </c>
       <c r="B187">
         <f>Sheet1!F187</f>
-        <v>44.05</v>
+        <v>11.75</v>
       </c>
       <c r="C187">
         <f>Sheet1!G187</f>
-        <v>13.5</v>
+        <v>50.5</v>
       </c>
       <c r="D187" t="str">
         <f>Sheet1!E187</f>
@@ -5863,17 +5869,17 @@
       </c>
       <c r="E187">
         <f>ROUND(Sheet1!H187,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="str">
         <f>Sheet1!A188</f>
-        <v>S404</v>
+        <v>S403</v>
       </c>
       <c r="B188">
         <f>Sheet1!F188</f>
-        <v>70.974999999999994</v>
+        <v>44.05</v>
       </c>
       <c r="C188">
         <f>Sheet1!G188</f>
@@ -5891,15 +5897,15 @@
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="str">
         <f>Sheet1!A189</f>
-        <v>S405</v>
+        <v>S404</v>
       </c>
       <c r="B189">
         <f>Sheet1!F189</f>
-        <v>103.25</v>
+        <v>70.974999999999994</v>
       </c>
       <c r="C189">
         <f>Sheet1!G189</f>
-        <v>58</v>
+        <v>13.5</v>
       </c>
       <c r="D189" t="str">
         <f>Sheet1!E189</f>
@@ -5907,13 +5913,13 @@
       </c>
       <c r="E189">
         <f>ROUND(Sheet1!H189,0)</f>
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="str">
         <f>Sheet1!A190</f>
-        <v>S406</v>
+        <v>S405</v>
       </c>
       <c r="B190">
         <f>Sheet1!F190</f>
@@ -5921,7 +5927,7 @@
       </c>
       <c r="C190">
         <f>Sheet1!G190</f>
-        <v>50.5</v>
+        <v>58</v>
       </c>
       <c r="D190" t="str">
         <f>Sheet1!E190</f>
@@ -5935,15 +5941,15 @@
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="str">
         <f>Sheet1!A191</f>
-        <v>U1</v>
+        <v>S406</v>
       </c>
       <c r="B191">
         <f>Sheet1!F191</f>
-        <v>12.6</v>
+        <v>103.25</v>
       </c>
       <c r="C191">
         <f>Sheet1!G191</f>
-        <v>36.75</v>
+        <v>50.5</v>
       </c>
       <c r="D191" t="str">
         <f>Sheet1!E191</f>
@@ -5951,21 +5957,21 @@
       </c>
       <c r="E191">
         <f>ROUND(Sheet1!H191,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="str">
         <f>Sheet1!A192</f>
-        <v>U2</v>
+        <v>U1</v>
       </c>
       <c r="B192">
         <f>Sheet1!F192</f>
-        <v>14.1</v>
+        <v>12.6</v>
       </c>
       <c r="C192">
         <f>Sheet1!G192</f>
-        <v>29.7</v>
+        <v>36.725000000000001</v>
       </c>
       <c r="D192" t="str">
         <f>Sheet1!E192</f>
@@ -5973,13 +5979,13 @@
       </c>
       <c r="E192">
         <f>ROUND(Sheet1!H192,0)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="str">
         <f>Sheet1!A193</f>
-        <v>U3</v>
+        <v>U2</v>
       </c>
       <c r="B193">
         <f>Sheet1!F193</f>
@@ -5987,7 +5993,7 @@
       </c>
       <c r="C193">
         <f>Sheet1!G193</f>
-        <v>21.4</v>
+        <v>29.7</v>
       </c>
       <c r="D193" t="str">
         <f>Sheet1!E193</f>
@@ -6001,7 +6007,7 @@
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="str">
         <f>Sheet1!A194</f>
-        <v>U4</v>
+        <v>U3</v>
       </c>
       <c r="B194">
         <f>Sheet1!F194</f>
@@ -6009,7 +6015,7 @@
       </c>
       <c r="C194">
         <f>Sheet1!G194</f>
-        <v>13.1</v>
+        <v>21.4</v>
       </c>
       <c r="D194" t="str">
         <f>Sheet1!E194</f>
@@ -6023,15 +6029,15 @@
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="str">
         <f>Sheet1!A195</f>
-        <v>U101</v>
+        <v>U4</v>
       </c>
       <c r="B195">
         <f>Sheet1!F195</f>
-        <v>57.5</v>
+        <v>14.1</v>
       </c>
       <c r="C195">
         <f>Sheet1!G195</f>
-        <v>50</v>
+        <v>13.1</v>
       </c>
       <c r="D195" t="str">
         <f>Sheet1!E195</f>
@@ -6045,7 +6051,7 @@
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="str">
         <f>Sheet1!A196</f>
-        <v>U102</v>
+        <v>U101</v>
       </c>
       <c r="B196">
         <f>Sheet1!F196</f>
@@ -6053,7 +6059,7 @@
       </c>
       <c r="C196">
         <f>Sheet1!G196</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D196" t="str">
         <f>Sheet1!E196</f>
@@ -6061,21 +6067,21 @@
       </c>
       <c r="E196">
         <f>ROUND(Sheet1!H196,0)</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="str">
         <f>Sheet1!A197</f>
-        <v>U103</v>
+        <v>U102</v>
       </c>
       <c r="B197">
         <f>Sheet1!F197</f>
-        <v>72.849999999999994</v>
+        <v>57.5</v>
       </c>
       <c r="C197">
         <f>Sheet1!G197</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D197" t="str">
         <f>Sheet1!E197</f>
@@ -6083,21 +6089,21 @@
       </c>
       <c r="E197">
         <f>ROUND(Sheet1!H197,0)</f>
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="str">
         <f>Sheet1!A198</f>
-        <v>U104</v>
+        <v>U103</v>
       </c>
       <c r="B198">
         <f>Sheet1!F198</f>
-        <v>96.85</v>
+        <v>72.849999999999994</v>
       </c>
       <c r="C198">
         <f>Sheet1!G198</f>
-        <v>30.25</v>
+        <v>32</v>
       </c>
       <c r="D198" t="str">
         <f>Sheet1!E198</f>
@@ -6111,15 +6117,15 @@
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="str">
         <f>Sheet1!A199</f>
-        <v>U301</v>
+        <v>U104</v>
       </c>
       <c r="B199">
         <f>Sheet1!F199</f>
-        <v>74.5</v>
+        <v>96.85</v>
       </c>
       <c r="C199">
         <f>Sheet1!G199</f>
-        <v>47</v>
+        <v>30.25</v>
       </c>
       <c r="D199" t="str">
         <f>Sheet1!E199</f>
@@ -6127,17 +6133,17 @@
       </c>
       <c r="E199">
         <f>ROUND(Sheet1!H199,0)</f>
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="str">
         <f>Sheet1!A200</f>
-        <v>U302</v>
+        <v>U301</v>
       </c>
       <c r="B200">
         <f>Sheet1!F200</f>
-        <v>82.5</v>
+        <v>74.5</v>
       </c>
       <c r="C200">
         <f>Sheet1!G200</f>
@@ -6155,11 +6161,11 @@
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="str">
         <f>Sheet1!A201</f>
-        <v>U303</v>
+        <v>U302</v>
       </c>
       <c r="B201">
         <f>Sheet1!F201</f>
-        <v>32.5</v>
+        <v>82.5</v>
       </c>
       <c r="C201">
         <f>Sheet1!G201</f>
@@ -6171,17 +6177,17 @@
       </c>
       <c r="E201">
         <f>ROUND(Sheet1!H201,0)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="str">
         <f>Sheet1!A202</f>
-        <v>U304</v>
+        <v>U303</v>
       </c>
       <c r="B202">
         <f>Sheet1!F202</f>
-        <v>40.5</v>
+        <v>32.5</v>
       </c>
       <c r="C202">
         <f>Sheet1!G202</f>
@@ -6199,15 +6205,15 @@
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="str">
         <f>Sheet1!A203</f>
-        <v>U601</v>
+        <v>U304</v>
       </c>
       <c r="B203">
         <f>Sheet1!F203</f>
-        <v>70.7</v>
+        <v>40.5</v>
       </c>
       <c r="C203">
         <f>Sheet1!G203</f>
-        <v>19.062999999999999</v>
+        <v>47</v>
       </c>
       <c r="D203" t="str">
         <f>Sheet1!E203</f>
@@ -6215,21 +6221,21 @@
       </c>
       <c r="E203">
         <f>ROUND(Sheet1!H203,0)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="str">
         <f>Sheet1!A204</f>
-        <v>U602</v>
+        <v>U601</v>
       </c>
       <c r="B204">
         <f>Sheet1!F204</f>
-        <v>83.8</v>
+        <v>70.7</v>
       </c>
       <c r="C204">
         <f>Sheet1!G204</f>
-        <v>19.75</v>
+        <v>19.062999999999999</v>
       </c>
       <c r="D204" t="str">
         <f>Sheet1!E204</f>
@@ -6237,21 +6243,21 @@
       </c>
       <c r="E204">
         <f>ROUND(Sheet1!H204,0)</f>
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="str">
         <f>Sheet1!A205</f>
-        <v>Y101</v>
+        <v>U602</v>
       </c>
       <c r="B205">
         <f>Sheet1!F205</f>
-        <v>47.25</v>
+        <v>83.8</v>
       </c>
       <c r="C205">
         <f>Sheet1!G205</f>
-        <v>50</v>
+        <v>19.75</v>
       </c>
       <c r="D205" t="str">
         <f>Sheet1!E205</f>
@@ -6259,6 +6265,28 @@
       </c>
       <c r="E205">
         <f>ROUND(Sheet1!H205,0)</f>
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="str">
+        <f>Sheet1!A206</f>
+        <v>Y101</v>
+      </c>
+      <c r="B206">
+        <f>Sheet1!F206</f>
+        <v>47.25</v>
+      </c>
+      <c r="C206">
+        <f>Sheet1!G206</f>
+        <v>50</v>
+      </c>
+      <c r="D206" t="str">
+        <f>Sheet1!E206</f>
+        <v>Top</v>
+      </c>
+      <c r="E206">
+        <f>ROUND(Sheet1!H206,0)</f>
         <v>-90</v>
       </c>
     </row>
@@ -6269,7 +6297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA15E41D-DBBC-4941-B2C8-EC6C9FECF311}">
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -6324,10 +6352,10 @@
         <v>11</v>
       </c>
       <c r="F2">
-        <v>15.8</v>
+        <v>12.6</v>
       </c>
       <c r="G2">
-        <v>37.700000000000003</v>
+        <v>34.274999999999999</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -6376,7 +6404,7 @@
         <v>11</v>
       </c>
       <c r="F4">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="G4">
         <v>34.424999999999997</v>
@@ -6480,7 +6508,7 @@
         <v>11</v>
       </c>
       <c r="F8">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="G8">
         <v>26.15</v>
@@ -6584,7 +6612,7 @@
         <v>11</v>
       </c>
       <c r="F12">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="G12">
         <v>17.824999999999999</v>
@@ -8701,13 +8729,13 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="B94" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C94" t="s">
-        <v>122</v>
+        <v>286</v>
       </c>
       <c r="D94" t="b">
         <v>1</v>
@@ -8716,24 +8744,24 @@
         <v>11</v>
       </c>
       <c r="F94">
-        <v>12.875</v>
+        <v>26.824999999999999</v>
       </c>
       <c r="G94">
-        <v>42.575000000000003</v>
+        <v>18.5</v>
       </c>
       <c r="H94">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B95" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C95" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D95" t="b">
         <v>1</v>
@@ -8742,10 +8770,10 @@
         <v>11</v>
       </c>
       <c r="F95">
-        <v>27.5</v>
+        <v>12.875</v>
       </c>
       <c r="G95">
-        <v>26</v>
+        <v>42.575000000000003</v>
       </c>
       <c r="H95">
         <v>-90</v>
@@ -8753,13 +8781,13 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B96" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C96" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D96" t="b">
         <v>1</v>
@@ -8768,114 +8796,114 @@
         <v>11</v>
       </c>
       <c r="F96">
-        <v>57.5</v>
+        <v>27.5</v>
       </c>
       <c r="G96">
-        <v>19.3</v>
+        <v>26</v>
       </c>
       <c r="H96">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B97" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C97" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D97" t="b">
         <v>1</v>
       </c>
       <c r="E97" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F97">
-        <v>17.5</v>
+        <v>57.5</v>
       </c>
       <c r="G97">
-        <v>48.5</v>
+        <v>19.3</v>
       </c>
       <c r="H97">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B98" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D98" t="b">
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F98">
-        <v>78.8</v>
+        <v>17.5</v>
       </c>
       <c r="G98">
-        <v>26.6</v>
+        <v>48.5</v>
       </c>
       <c r="H98">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B99" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C99" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D99" t="b">
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F99">
-        <v>97.5</v>
+        <v>78.8</v>
       </c>
       <c r="G99">
-        <v>48.5</v>
+        <v>26.6</v>
       </c>
       <c r="H99">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B100" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C100" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D100" t="b">
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F100">
-        <v>101.797</v>
+        <v>97.5</v>
       </c>
       <c r="G100">
-        <v>17.100000000000001</v>
+        <v>48.5</v>
       </c>
       <c r="H100">
         <v>-90</v>
@@ -8883,13 +8911,13 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B101" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C101" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D101" t="b">
         <v>1</v>
@@ -8898,122 +8926,122 @@
         <v>11</v>
       </c>
       <c r="F101">
-        <v>36.200000000000003</v>
+        <v>101.797</v>
       </c>
       <c r="G101">
-        <v>26.6</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="H101">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B102" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C102" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D102" t="b">
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F102">
-        <v>32.5</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="G102">
-        <v>14.5</v>
+        <v>26.6</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C103" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D103" t="b">
         <v>1</v>
       </c>
       <c r="E103" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F103">
-        <v>103.25</v>
+        <v>32.5</v>
       </c>
       <c r="G103">
-        <v>41.55</v>
+        <v>14.5</v>
       </c>
       <c r="H103">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B104" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D104" t="b">
         <v>1</v>
       </c>
       <c r="E104" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F104">
-        <v>82.5</v>
+        <v>103.25</v>
       </c>
       <c r="G104">
-        <v>14.5</v>
+        <v>41.55</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B105" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C105" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D105" t="b">
         <v>1</v>
       </c>
       <c r="E105" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F105">
-        <v>50.75</v>
+        <v>82.5</v>
       </c>
       <c r="G105">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="H105">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B106" t="s">
         <v>143</v>
@@ -9028,7 +9056,7 @@
         <v>11</v>
       </c>
       <c r="F106">
-        <v>64.25</v>
+        <v>50.75</v>
       </c>
       <c r="G106">
         <v>13.5</v>
@@ -9039,13 +9067,13 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B107" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C107" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D107" t="b">
         <v>1</v>
@@ -9054,18 +9082,18 @@
         <v>11</v>
       </c>
       <c r="F107">
-        <v>17.600000000000001</v>
+        <v>64.25</v>
       </c>
       <c r="G107">
-        <v>29.5</v>
+        <v>13.5</v>
       </c>
       <c r="H107">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B108" t="s">
         <v>147</v>
@@ -9083,7 +9111,7 @@
         <v>17.600000000000001</v>
       </c>
       <c r="G108">
-        <v>21.2</v>
+        <v>29.5</v>
       </c>
       <c r="H108">
         <v>90</v>
@@ -9091,7 +9119,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B109" t="s">
         <v>147</v>
@@ -9109,7 +9137,7 @@
         <v>17.600000000000001</v>
       </c>
       <c r="G109">
-        <v>12.9</v>
+        <v>21.2</v>
       </c>
       <c r="H109">
         <v>90</v>
@@ -9117,13 +9145,13 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B110" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C110" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D110" t="b">
         <v>1</v>
@@ -9132,36 +9160,36 @@
         <v>11</v>
       </c>
       <c r="F110">
-        <v>51.1</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="G110">
-        <v>51.225000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="H110">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B111" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C111" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D111" t="b">
         <v>1</v>
       </c>
       <c r="E111" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F111">
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="G111">
-        <v>13.5</v>
+        <v>51.225000000000001</v>
       </c>
       <c r="H111">
         <v>-90</v>
@@ -9169,33 +9197,33 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B112" t="s">
         <v>155</v>
       </c>
       <c r="C112" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D112" t="b">
         <v>1</v>
       </c>
       <c r="E112" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F112">
-        <v>21.1</v>
+        <v>46.5</v>
       </c>
       <c r="G112">
-        <v>16.7</v>
+        <v>13.5</v>
       </c>
       <c r="H112">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B113" t="s">
         <v>155</v>
@@ -9210,10 +9238,10 @@
         <v>11</v>
       </c>
       <c r="F113">
-        <v>21.15</v>
+        <v>21.1</v>
       </c>
       <c r="G113">
-        <v>12.95</v>
+        <v>16.7</v>
       </c>
       <c r="H113">
         <v>90</v>
@@ -9221,13 +9249,13 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B114" t="s">
         <v>155</v>
       </c>
       <c r="C114" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D114" t="b">
         <v>1</v>
@@ -9236,18 +9264,18 @@
         <v>11</v>
       </c>
       <c r="F114">
-        <v>48.475000000000001</v>
+        <v>21.15</v>
       </c>
       <c r="G114">
-        <v>26.425000000000001</v>
+        <v>12.95</v>
       </c>
       <c r="H114">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B115" t="s">
         <v>155</v>
@@ -9265,21 +9293,21 @@
         <v>48.475000000000001</v>
       </c>
       <c r="G115">
-        <v>28.225000000000001</v>
+        <v>26.425000000000001</v>
       </c>
       <c r="H115">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B116" t="s">
         <v>155</v>
       </c>
       <c r="C116" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D116" t="b">
         <v>1</v>
@@ -9288,24 +9316,24 @@
         <v>11</v>
       </c>
       <c r="F116">
-        <v>14.1</v>
+        <v>48.475000000000001</v>
       </c>
       <c r="G116">
-        <v>32.450000000000003</v>
+        <v>28.225000000000001</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B117" t="s">
         <v>155</v>
       </c>
       <c r="C117" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D117" t="b">
         <v>1</v>
@@ -9314,10 +9342,10 @@
         <v>11</v>
       </c>
       <c r="F117">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="G117">
-        <v>33.450000000000003</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -9325,7 +9353,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B118" t="s">
         <v>155</v>
@@ -9340,24 +9368,24 @@
         <v>11</v>
       </c>
       <c r="F118">
-        <v>12.1</v>
+        <v>14.6</v>
       </c>
       <c r="G118">
-        <v>32.450000000000003</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="H118">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B119" t="s">
         <v>155</v>
       </c>
       <c r="C119" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D119" t="b">
         <v>1</v>
@@ -9366,18 +9394,18 @@
         <v>11</v>
       </c>
       <c r="F119">
-        <v>14.1</v>
+        <v>12.6</v>
       </c>
       <c r="G119">
-        <v>24.15</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B120" t="s">
         <v>155</v>
@@ -9392,10 +9420,10 @@
         <v>11</v>
       </c>
       <c r="F120">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="G120">
-        <v>25.15</v>
+        <v>24.15</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -9403,13 +9431,13 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B121" t="s">
         <v>155</v>
       </c>
       <c r="C121" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D121" t="b">
         <v>1</v>
@@ -9418,24 +9446,24 @@
         <v>11</v>
       </c>
       <c r="F121">
-        <v>12.1</v>
+        <v>14.6</v>
       </c>
       <c r="G121">
-        <v>24.15</v>
+        <v>25.15</v>
       </c>
       <c r="H121">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B122" t="s">
         <v>155</v>
       </c>
       <c r="C122" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D122" t="b">
         <v>1</v>
@@ -9444,18 +9472,18 @@
         <v>11</v>
       </c>
       <c r="F122">
-        <v>14.1</v>
+        <v>12.6</v>
       </c>
       <c r="G122">
-        <v>15.85</v>
+        <v>24.15</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B123" t="s">
         <v>155</v>
@@ -9470,10 +9498,10 @@
         <v>11</v>
       </c>
       <c r="F123">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="G123">
-        <v>16.850000000000001</v>
+        <v>15.85</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -9481,13 +9509,13 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B124" t="s">
         <v>155</v>
       </c>
       <c r="C124" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D124" t="b">
         <v>1</v>
@@ -9496,24 +9524,24 @@
         <v>11</v>
       </c>
       <c r="F124">
-        <v>12.1</v>
+        <v>14.6</v>
       </c>
       <c r="G124">
-        <v>15.85</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="H124">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B125" t="s">
         <v>155</v>
       </c>
       <c r="C125" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D125" t="b">
         <v>1</v>
@@ -9522,44 +9550,44 @@
         <v>11</v>
       </c>
       <c r="F125">
-        <v>51.1</v>
+        <v>12.6</v>
       </c>
       <c r="G125">
-        <v>48.55</v>
+        <v>15.85</v>
       </c>
       <c r="H125">
-        <v>90.01</v>
+        <v>180</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B126" t="s">
         <v>155</v>
       </c>
       <c r="C126" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D126" t="b">
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F126">
-        <v>50.35</v>
+        <v>51.1</v>
       </c>
       <c r="G126">
-        <v>53.174999999999997</v>
+        <v>48.55</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>90.01</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B127" t="s">
         <v>155</v>
@@ -9571,73 +9599,73 @@
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F127">
-        <v>65.525000000000006</v>
+        <v>50.35</v>
       </c>
       <c r="G127">
-        <v>53.575000000000003</v>
+        <v>53.174999999999997</v>
       </c>
       <c r="H127">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B128" t="s">
         <v>155</v>
       </c>
       <c r="C128" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D128" t="b">
         <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F128">
-        <v>53.274999999999999</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="G128">
-        <v>48.375</v>
+        <v>53.575000000000003</v>
       </c>
       <c r="H128">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B129" t="s">
         <v>155</v>
       </c>
       <c r="C129" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D129" t="b">
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F129">
-        <v>74.900000000000006</v>
+        <v>53.274999999999999</v>
       </c>
       <c r="G129">
-        <v>32.549999999999997</v>
+        <v>48.375</v>
       </c>
       <c r="H129">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B130" t="s">
         <v>155</v>
@@ -9655,7 +9683,7 @@
         <v>74.900000000000006</v>
       </c>
       <c r="G130">
-        <v>33.450000000000003</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="H130">
         <v>180</v>
@@ -9663,13 +9691,13 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B131" t="s">
         <v>155</v>
       </c>
       <c r="C131" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="D131" t="b">
         <v>1</v>
@@ -9678,50 +9706,50 @@
         <v>11</v>
       </c>
       <c r="F131">
-        <v>75.2</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="G131">
-        <v>29.05</v>
+        <v>33.450000000000003</v>
       </c>
       <c r="H131">
-        <v>90.01</v>
+        <v>180</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B132" t="s">
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="D132" t="b">
         <v>1</v>
       </c>
       <c r="E132" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F132">
-        <v>66.8</v>
+        <v>75.2</v>
       </c>
       <c r="G132">
-        <v>31.3</v>
+        <v>29.05</v>
       </c>
       <c r="H132">
-        <v>-90</v>
+        <v>90.01</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B133" t="s">
         <v>155</v>
       </c>
       <c r="C133" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="D133" t="b">
         <v>1</v>
@@ -9730,24 +9758,24 @@
         <v>32</v>
       </c>
       <c r="F133">
-        <v>63.9</v>
+        <v>66.8</v>
       </c>
       <c r="G133">
-        <v>35.5</v>
+        <v>31.3</v>
       </c>
       <c r="H133">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B134" t="s">
         <v>155</v>
       </c>
       <c r="C134" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="D134" t="b">
         <v>1</v>
@@ -9756,18 +9784,18 @@
         <v>32</v>
       </c>
       <c r="F134">
-        <v>45.4</v>
+        <v>63.9</v>
       </c>
       <c r="G134">
-        <v>28.3</v>
+        <v>35.5</v>
       </c>
       <c r="H134">
-        <v>0.01</v>
+        <v>90</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B135" t="s">
         <v>155</v>
@@ -9785,7 +9813,7 @@
         <v>45.4</v>
       </c>
       <c r="G135">
-        <v>33.1</v>
+        <v>28.3</v>
       </c>
       <c r="H135">
         <v>0.01</v>
@@ -9793,13 +9821,13 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B136" t="s">
         <v>155</v>
       </c>
       <c r="C136" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="D136" t="b">
         <v>1</v>
@@ -9808,18 +9836,18 @@
         <v>32</v>
       </c>
       <c r="F136">
-        <v>60.7</v>
+        <v>45.4</v>
       </c>
       <c r="G136">
-        <v>36.75</v>
+        <v>33.1</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B137" t="s">
         <v>155</v>
@@ -9831,13 +9859,13 @@
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F137">
-        <v>86.5</v>
+        <v>60.7</v>
       </c>
       <c r="G137">
-        <v>26.25</v>
+        <v>36.75</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -9845,33 +9873,33 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B138" t="s">
         <v>155</v>
       </c>
       <c r="C138" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D138" t="b">
         <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F138">
-        <v>45.4</v>
+        <v>86.5</v>
       </c>
       <c r="G138">
-        <v>30</v>
+        <v>26.25</v>
       </c>
       <c r="H138">
-        <v>-179.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B139" t="s">
         <v>155</v>
@@ -9886,44 +9914,44 @@
         <v>32</v>
       </c>
       <c r="F139">
-        <v>66.8</v>
+        <v>45.4</v>
       </c>
       <c r="G139">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H139">
-        <v>-90</v>
+        <v>-179.99</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B140" t="s">
         <v>155</v>
       </c>
       <c r="C140" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="D140" t="b">
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F140">
-        <v>86.5</v>
+        <v>66.8</v>
       </c>
       <c r="G140">
-        <v>28.75</v>
+        <v>28</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B141" t="s">
         <v>155</v>
@@ -9941,7 +9969,7 @@
         <v>86.5</v>
       </c>
       <c r="G141">
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="H141">
         <v>0</v>
@@ -9949,33 +9977,33 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B142" t="s">
         <v>155</v>
       </c>
       <c r="C142" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="D142" t="b">
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F142">
-        <v>71.900000000000006</v>
+        <v>86.5</v>
       </c>
       <c r="G142">
-        <v>37.200000000000003</v>
+        <v>27.75</v>
       </c>
       <c r="H142">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B143" t="s">
         <v>155</v>
@@ -9990,10 +10018,10 @@
         <v>32</v>
       </c>
       <c r="F143">
-        <v>71.3</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="G143">
-        <v>35.25</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="H143">
         <v>-90</v>
@@ -10001,7 +10029,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B144" t="s">
         <v>155</v>
@@ -10016,7 +10044,7 @@
         <v>32</v>
       </c>
       <c r="F144">
-        <v>72.5</v>
+        <v>71.3</v>
       </c>
       <c r="G144">
         <v>35.25</v>
@@ -10027,33 +10055,33 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B145" t="s">
         <v>155</v>
       </c>
       <c r="C145" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="D145" t="b">
         <v>1</v>
       </c>
       <c r="E145" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F145">
-        <v>86.5</v>
+        <v>72.5</v>
       </c>
       <c r="G145">
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B146" t="s">
         <v>155</v>
@@ -10068,44 +10096,44 @@
         <v>11</v>
       </c>
       <c r="F146">
-        <v>72.05</v>
+        <v>86.5</v>
       </c>
       <c r="G146">
-        <v>29.05</v>
+        <v>34.25</v>
       </c>
       <c r="H146">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B147" t="s">
         <v>155</v>
       </c>
       <c r="C147" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="D147" t="b">
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F147">
-        <v>73.099999999999994</v>
+        <v>72.05</v>
       </c>
       <c r="G147">
-        <v>37.200000000000003</v>
+        <v>29.05</v>
       </c>
       <c r="H147">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B148" t="s">
         <v>155</v>
@@ -10120,7 +10148,7 @@
         <v>32</v>
       </c>
       <c r="F148">
-        <v>70.7</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="G148">
         <v>37.200000000000003</v>
@@ -10131,25 +10159,25 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B149" t="s">
         <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="D149" t="b">
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F149">
-        <v>75.25</v>
+        <v>70.7</v>
       </c>
       <c r="G149">
-        <v>23.324999999999999</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="H149">
         <v>-90</v>
@@ -10157,33 +10185,33 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B150" t="s">
         <v>155</v>
       </c>
       <c r="C150" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D150" t="b">
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F150">
-        <v>57.35</v>
+        <v>75.25</v>
       </c>
       <c r="G150">
-        <v>37.200000000000003</v>
+        <v>23.324999999999999</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B151" t="s">
         <v>155</v>
@@ -10198,44 +10226,44 @@
         <v>32</v>
       </c>
       <c r="F151">
-        <v>64.7</v>
+        <v>57.35</v>
       </c>
       <c r="G151">
-        <v>22.8</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="H151">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B152" t="s">
         <v>155</v>
       </c>
       <c r="C152" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="D152" t="b">
         <v>1</v>
       </c>
       <c r="E152" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F152">
-        <v>73.099999999999994</v>
+        <v>64.7</v>
       </c>
       <c r="G152">
-        <v>29.05</v>
+        <v>22.8</v>
       </c>
       <c r="H152">
-        <v>90.01</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B153" t="s">
         <v>155</v>
@@ -10250,24 +10278,24 @@
         <v>11</v>
       </c>
       <c r="F153">
-        <v>92</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="G153">
-        <v>38</v>
+        <v>29.05</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>90.01</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B154" t="s">
         <v>155</v>
       </c>
       <c r="C154" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="D154" t="b">
         <v>1</v>
@@ -10276,24 +10304,24 @@
         <v>11</v>
       </c>
       <c r="F154">
-        <v>73.099999999999994</v>
+        <v>92</v>
       </c>
       <c r="G154">
-        <v>34.4</v>
+        <v>38</v>
       </c>
       <c r="H154">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B155" t="s">
         <v>155</v>
       </c>
       <c r="C155" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="D155" t="b">
         <v>1</v>
@@ -10302,7 +10330,7 @@
         <v>11</v>
       </c>
       <c r="F155">
-        <v>74.900000000000006</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="G155">
         <v>34.4</v>
@@ -10313,13 +10341,13 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B156" t="s">
         <v>155</v>
       </c>
       <c r="C156" t="s">
-        <v>197</v>
+        <v>161</v>
       </c>
       <c r="D156" t="b">
         <v>1</v>
@@ -10328,18 +10356,18 @@
         <v>11</v>
       </c>
       <c r="F156">
-        <v>86.5</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="G156">
-        <v>31.15</v>
+        <v>34.4</v>
       </c>
       <c r="H156">
-        <v>180</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B157" t="s">
         <v>155</v>
@@ -10357,7 +10385,7 @@
         <v>86.5</v>
       </c>
       <c r="G157">
-        <v>30.15</v>
+        <v>31.15</v>
       </c>
       <c r="H157">
         <v>180</v>
@@ -10365,59 +10393,59 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B158" t="s">
         <v>155</v>
       </c>
       <c r="C158" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="D158" t="b">
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F158">
-        <v>94</v>
+        <v>86.5</v>
       </c>
       <c r="G158">
-        <v>24.15</v>
+        <v>30.15</v>
       </c>
       <c r="H158">
-        <v>-90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B159" t="s">
         <v>155</v>
       </c>
       <c r="C159" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="D159" t="b">
         <v>1</v>
       </c>
       <c r="E159" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F159">
-        <v>48.4</v>
+        <v>94</v>
       </c>
       <c r="G159">
-        <v>47.15</v>
+        <v>24.15</v>
       </c>
       <c r="H159">
-        <v>180</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B160" t="s">
         <v>155</v>
@@ -10435,7 +10463,7 @@
         <v>48.4</v>
       </c>
       <c r="G160">
-        <v>46</v>
+        <v>47.15</v>
       </c>
       <c r="H160">
         <v>180</v>
@@ -10443,13 +10471,13 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B161" t="s">
         <v>155</v>
       </c>
       <c r="C161" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="D161" t="b">
         <v>1</v>
@@ -10458,18 +10486,18 @@
         <v>11</v>
       </c>
       <c r="F161">
-        <v>31.3</v>
+        <v>48.4</v>
       </c>
       <c r="G161">
-        <v>32.450000000000003</v>
+        <v>46</v>
       </c>
       <c r="H161">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B162" t="s">
         <v>155</v>
@@ -10484,10 +10512,10 @@
         <v>11</v>
       </c>
       <c r="F162">
-        <v>82.45</v>
+        <v>31.3</v>
       </c>
       <c r="G162">
-        <v>23.324999999999999</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="H162">
         <v>90</v>
@@ -10495,7 +10523,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B163" t="s">
         <v>155</v>
@@ -10510,10 +10538,10 @@
         <v>11</v>
       </c>
       <c r="F163">
-        <v>32.5</v>
+        <v>82.45</v>
       </c>
       <c r="G163">
-        <v>23.45</v>
+        <v>23.324999999999999</v>
       </c>
       <c r="H163">
         <v>90</v>
@@ -10521,13 +10549,13 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B164" t="s">
         <v>155</v>
       </c>
       <c r="C164" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D164" t="b">
         <v>1</v>
@@ -10536,36 +10564,36 @@
         <v>11</v>
       </c>
       <c r="F164">
-        <v>26.125</v>
+        <v>32.5</v>
       </c>
       <c r="G164">
-        <v>21.875</v>
+        <v>23.45</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B165" t="s">
         <v>155</v>
       </c>
       <c r="C165" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="D165" t="b">
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F165">
-        <v>14.025</v>
+        <v>26.125</v>
       </c>
       <c r="G165">
-        <v>58.3</v>
+        <v>21.875</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -10573,25 +10601,25 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B166" t="s">
-        <v>222</v>
+        <v>155</v>
       </c>
       <c r="C166" t="s">
-        <v>223</v>
+        <v>161</v>
       </c>
       <c r="D166" t="b">
         <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F166">
-        <v>95.9</v>
+        <v>14.025</v>
       </c>
       <c r="G166">
-        <v>20.2</v>
+        <v>58.3</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -10599,13 +10627,13 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B167" t="s">
-        <v>155</v>
+        <v>222</v>
       </c>
       <c r="C167" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="D167" t="b">
         <v>1</v>
@@ -10614,44 +10642,44 @@
         <v>11</v>
       </c>
       <c r="F167">
-        <v>86.5</v>
+        <v>95.9</v>
       </c>
       <c r="G167">
-        <v>25.25</v>
+        <v>20.2</v>
       </c>
       <c r="H167">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B168" t="s">
         <v>155</v>
       </c>
       <c r="C168" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D168" t="b">
         <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F168">
-        <v>103.88500000000001</v>
+        <v>86.5</v>
       </c>
       <c r="G168">
-        <v>41.55</v>
+        <v>25.25</v>
       </c>
       <c r="H168">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B169" t="s">
         <v>155</v>
@@ -10666,7 +10694,7 @@
         <v>32</v>
       </c>
       <c r="F169">
-        <v>102.61499999999999</v>
+        <v>103.88500000000001</v>
       </c>
       <c r="G169">
         <v>41.55</v>
@@ -10677,33 +10705,33 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B170" t="s">
         <v>155</v>
       </c>
       <c r="C170" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D170" t="b">
         <v>1</v>
       </c>
       <c r="E170" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F170">
-        <v>11.75</v>
+        <v>102.61499999999999</v>
       </c>
       <c r="G170">
-        <v>61.125</v>
+        <v>41.55</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B171" t="s">
         <v>155</v>
@@ -10715,21 +10743,21 @@
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F171">
-        <v>44.35</v>
+        <v>11.75</v>
       </c>
       <c r="G171">
-        <v>15.9</v>
+        <v>61.125</v>
       </c>
       <c r="H171">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B172" t="s">
         <v>155</v>
@@ -10744,10 +10772,10 @@
         <v>32</v>
       </c>
       <c r="F172">
-        <v>70.924999999999997</v>
+        <v>44.35</v>
       </c>
       <c r="G172">
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="H172">
         <v>90</v>
@@ -10755,33 +10783,33 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B173" t="s">
         <v>155</v>
       </c>
       <c r="C173" t="s">
-        <v>231</v>
+        <v>161</v>
       </c>
       <c r="D173" t="b">
         <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F173">
-        <v>50.75</v>
+        <v>70.924999999999997</v>
       </c>
       <c r="G173">
-        <v>16.024999999999999</v>
+        <v>16.3</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B174" t="s">
         <v>155</v>
@@ -10796,18 +10824,18 @@
         <v>11</v>
       </c>
       <c r="F174">
-        <v>66</v>
+        <v>50.75</v>
       </c>
       <c r="G174">
-        <v>17</v>
+        <v>16.024999999999999</v>
       </c>
       <c r="H174">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B175" t="s">
         <v>155</v>
@@ -10822,18 +10850,18 @@
         <v>11</v>
       </c>
       <c r="F175">
-        <v>49.024999999999999</v>
+        <v>66</v>
       </c>
       <c r="G175">
         <v>17</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B176" t="s">
         <v>155</v>
@@ -10848,24 +10876,24 @@
         <v>11</v>
       </c>
       <c r="F176">
-        <v>64.25</v>
+        <v>49.024999999999999</v>
       </c>
       <c r="G176">
-        <v>16.024999999999999</v>
+        <v>17</v>
       </c>
       <c r="H176">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B177" t="s">
         <v>155</v>
       </c>
       <c r="C177" t="s">
-        <v>161</v>
+        <v>231</v>
       </c>
       <c r="D177" t="b">
         <v>1</v>
@@ -10874,18 +10902,18 @@
         <v>11</v>
       </c>
       <c r="F177">
-        <v>72.7</v>
+        <v>64.25</v>
       </c>
       <c r="G177">
-        <v>21.45</v>
+        <v>16.024999999999999</v>
       </c>
       <c r="H177">
-        <v>90</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B178" t="s">
         <v>155</v>
@@ -10900,24 +10928,24 @@
         <v>11</v>
       </c>
       <c r="F178">
-        <v>86.2</v>
+        <v>72.7</v>
       </c>
       <c r="G178">
-        <v>17.75</v>
+        <v>21.45</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B179" t="s">
         <v>155</v>
       </c>
       <c r="C179" t="s">
-        <v>238</v>
+        <v>161</v>
       </c>
       <c r="D179" t="b">
         <v>1</v>
@@ -10926,24 +10954,24 @@
         <v>11</v>
       </c>
       <c r="F179">
-        <v>68.7</v>
+        <v>86.2</v>
       </c>
       <c r="G179">
-        <v>21.45</v>
+        <v>17.75</v>
       </c>
       <c r="H179">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B180" t="s">
         <v>155</v>
       </c>
       <c r="C180" t="s">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="D180" t="b">
         <v>1</v>
@@ -10952,24 +10980,24 @@
         <v>11</v>
       </c>
       <c r="F180">
-        <v>69.7</v>
+        <v>68.7</v>
       </c>
       <c r="G180">
         <v>21.45</v>
       </c>
       <c r="H180">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B181" t="s">
         <v>155</v>
       </c>
       <c r="C181" t="s">
-        <v>238</v>
+        <v>161</v>
       </c>
       <c r="D181" t="b">
         <v>1</v>
@@ -10978,24 +11006,24 @@
         <v>11</v>
       </c>
       <c r="F181">
-        <v>86.2</v>
+        <v>69.7</v>
       </c>
       <c r="G181">
-        <v>21.65</v>
+        <v>21.45</v>
       </c>
       <c r="H181">
-        <v>180</v>
+        <v>90</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B182" t="s">
         <v>155</v>
       </c>
       <c r="C182" t="s">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="D182" t="b">
         <v>1</v>
@@ -11007,21 +11035,21 @@
         <v>86.2</v>
       </c>
       <c r="G182">
-        <v>20.7</v>
+        <v>21.65</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B183" t="s">
         <v>155</v>
       </c>
       <c r="C183" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="D183" t="b">
         <v>1</v>
@@ -11030,18 +11058,18 @@
         <v>11</v>
       </c>
       <c r="F183">
-        <v>51.45</v>
+        <v>86.2</v>
       </c>
       <c r="G183">
-        <v>10.75</v>
+        <v>20.7</v>
       </c>
       <c r="H183">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B184" t="s">
         <v>155</v>
@@ -11056,24 +11084,24 @@
         <v>11</v>
       </c>
       <c r="F184">
-        <v>63.55</v>
+        <v>51.45</v>
       </c>
       <c r="G184">
         <v>10.75</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B185" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="C185" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="D185" t="b">
         <v>1</v>
@@ -11082,18 +11110,18 @@
         <v>11</v>
       </c>
       <c r="F185">
-        <v>11.75</v>
+        <v>63.55</v>
       </c>
       <c r="G185">
-        <v>58</v>
+        <v>10.75</v>
       </c>
       <c r="H185">
-        <v>90.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B186" t="s">
         <v>121</v>
@@ -11111,15 +11139,15 @@
         <v>11.75</v>
       </c>
       <c r="G186">
-        <v>50.5</v>
+        <v>58</v>
       </c>
       <c r="H186">
-        <v>90</v>
+        <v>90.01</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B187" t="s">
         <v>121</v>
@@ -11134,18 +11162,18 @@
         <v>11</v>
       </c>
       <c r="F187">
-        <v>44.05</v>
+        <v>11.75</v>
       </c>
       <c r="G187">
-        <v>13.5</v>
+        <v>50.5</v>
       </c>
       <c r="H187">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B188" t="s">
         <v>121</v>
@@ -11160,7 +11188,7 @@
         <v>11</v>
       </c>
       <c r="F188">
-        <v>70.974999999999994</v>
+        <v>44.05</v>
       </c>
       <c r="G188">
         <v>13.5</v>
@@ -11171,7 +11199,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B189" t="s">
         <v>121</v>
@@ -11186,18 +11214,18 @@
         <v>11</v>
       </c>
       <c r="F189">
-        <v>103.25</v>
+        <v>70.974999999999994</v>
       </c>
       <c r="G189">
-        <v>58</v>
+        <v>13.5</v>
       </c>
       <c r="H189">
-        <v>90</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B190" t="s">
         <v>121</v>
@@ -11215,7 +11243,7 @@
         <v>103.25</v>
       </c>
       <c r="G190">
-        <v>50.5</v>
+        <v>58</v>
       </c>
       <c r="H190">
         <v>90</v>
@@ -11223,13 +11251,13 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B191" t="s">
-        <v>252</v>
+        <v>121</v>
       </c>
       <c r="C191" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D191" t="b">
         <v>1</v>
@@ -11238,24 +11266,24 @@
         <v>11</v>
       </c>
       <c r="F191">
-        <v>12.6</v>
+        <v>103.25</v>
       </c>
       <c r="G191">
-        <v>36.75</v>
+        <v>50.5</v>
       </c>
       <c r="H191">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B192" t="s">
         <v>252</v>
       </c>
       <c r="C192" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D192" t="b">
         <v>1</v>
@@ -11264,18 +11292,18 @@
         <v>11</v>
       </c>
       <c r="F192">
-        <v>14.1</v>
+        <v>12.6</v>
       </c>
       <c r="G192">
-        <v>29.7</v>
+        <v>36.725000000000001</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B193" t="s">
         <v>252</v>
@@ -11293,7 +11321,7 @@
         <v>14.1</v>
       </c>
       <c r="G193">
-        <v>21.4</v>
+        <v>29.7</v>
       </c>
       <c r="H193">
         <v>0</v>
@@ -11301,7 +11329,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B194" t="s">
         <v>252</v>
@@ -11319,7 +11347,7 @@
         <v>14.1</v>
       </c>
       <c r="G194">
-        <v>13.1</v>
+        <v>21.4</v>
       </c>
       <c r="H194">
         <v>0</v>
@@ -11327,13 +11355,13 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B195" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C195" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D195" t="b">
         <v>1</v>
@@ -11342,10 +11370,10 @@
         <v>11</v>
       </c>
       <c r="F195">
-        <v>57.5</v>
+        <v>14.1</v>
       </c>
       <c r="G195">
-        <v>50</v>
+        <v>13.1</v>
       </c>
       <c r="H195">
         <v>0</v>
@@ -11353,13 +11381,13 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B196" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D196" t="b">
         <v>1</v>
@@ -11371,21 +11399,21 @@
         <v>57.5</v>
       </c>
       <c r="G196">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H196">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B197" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C197" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D197" t="b">
         <v>1</v>
@@ -11394,24 +11422,24 @@
         <v>11</v>
       </c>
       <c r="F197">
-        <v>72.849999999999994</v>
+        <v>57.5</v>
       </c>
       <c r="G197">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H197">
-        <v>-90</v>
+        <v>90</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B198" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C198" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D198" t="b">
         <v>1</v>
@@ -11420,10 +11448,10 @@
         <v>11</v>
       </c>
       <c r="F198">
-        <v>96.85</v>
+        <v>72.849999999999994</v>
       </c>
       <c r="G198">
-        <v>30.25</v>
+        <v>32</v>
       </c>
       <c r="H198">
         <v>-90</v>
@@ -11431,13 +11459,13 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B199" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C199" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D199" t="b">
         <v>1</v>
@@ -11446,18 +11474,18 @@
         <v>11</v>
       </c>
       <c r="F199">
-        <v>74.5</v>
+        <v>96.85</v>
       </c>
       <c r="G199">
-        <v>47</v>
+        <v>30.25</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B200" t="s">
         <v>252</v>
@@ -11472,7 +11500,7 @@
         <v>11</v>
       </c>
       <c r="F200">
-        <v>82.5</v>
+        <v>74.5</v>
       </c>
       <c r="G200">
         <v>47</v>
@@ -11483,7 +11511,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B201" t="s">
         <v>252</v>
@@ -11498,18 +11526,18 @@
         <v>11</v>
       </c>
       <c r="F201">
-        <v>32.5</v>
+        <v>82.5</v>
       </c>
       <c r="G201">
         <v>47</v>
       </c>
       <c r="H201">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B202" t="s">
         <v>252</v>
@@ -11524,7 +11552,7 @@
         <v>11</v>
       </c>
       <c r="F202">
-        <v>40.5</v>
+        <v>32.5</v>
       </c>
       <c r="G202">
         <v>47</v>
@@ -11535,13 +11563,13 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B203" t="s">
         <v>252</v>
       </c>
       <c r="C203" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D203" t="b">
         <v>1</v>
@@ -11550,18 +11578,18 @@
         <v>11</v>
       </c>
       <c r="F203">
-        <v>70.7</v>
+        <v>40.5</v>
       </c>
       <c r="G203">
-        <v>19.062999999999999</v>
+        <v>47</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B204" t="s">
         <v>252</v>
@@ -11576,38 +11604,64 @@
         <v>11</v>
       </c>
       <c r="F204">
-        <v>83.8</v>
+        <v>70.7</v>
       </c>
       <c r="G204">
-        <v>19.75</v>
+        <v>19.062999999999999</v>
       </c>
       <c r="H204">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>277</v>
+      </c>
+      <c r="B205" t="s">
+        <v>252</v>
+      </c>
+      <c r="C205" t="s">
+        <v>276</v>
+      </c>
+      <c r="D205" t="b">
+        <v>1</v>
+      </c>
+      <c r="E205" t="s">
+        <v>11</v>
+      </c>
+      <c r="F205">
+        <v>83.8</v>
+      </c>
+      <c r="G205">
+        <v>19.75</v>
+      </c>
+      <c r="H205">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
         <v>278</v>
       </c>
-      <c r="B205" t="s">
+      <c r="B206" t="s">
         <v>279</v>
       </c>
-      <c r="C205" t="s">
+      <c r="C206" t="s">
         <v>280</v>
       </c>
-      <c r="D205" t="b">
-        <v>1</v>
-      </c>
-      <c r="E205" t="s">
-        <v>11</v>
-      </c>
-      <c r="F205">
+      <c r="D206" t="b">
+        <v>1</v>
+      </c>
+      <c r="E206" t="s">
+        <v>11</v>
+      </c>
+      <c r="F206">
         <v>47.25</v>
       </c>
-      <c r="G205">
+      <c r="G206">
         <v>50</v>
       </c>
-      <c r="H205">
+      <c r="H206">
         <v>-90</v>
       </c>
     </row>
